--- a/data/roadmap_estudi_so.xlsx
+++ b/data/roadmap_estudi_so.xlsx
@@ -417,67 +417,66 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Roadmap de recursos — Estudi de so (Producció, Gravació, Edició, Mescla, Disseny de so, Harmonia, Llenguatge musical)</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Com utilitzar aquest Excel</v>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Com utilitzar aquest Excel</v>
+        <v>1) Comença per 'Fonaments transversals' i després segueix les categories segons els teus objectius.</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>1) Comença per 'Fonaments transversals' i després segueix les categories segons els teus objectius.</v>
+        <v>2) Cada fila és un tema. La columna 'Prerequisits (IDs)' indica què convé dominar abans.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2) Cada fila és un tema. La columna 'Prerequisits (IDs)' indica què convé dominar abans.</v>
+        <v>3) 'Tipus de recurs' suggereix el format ideal (article, tutorial, checklist, plantilla, projecte).</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3) 'Tipus de recurs' suggereix el format ideal (article, tutorial, checklist, plantilla, projecte).</v>
+        <v>4) 'Monetització suggerida' + 'CTA suggerida' t'ajuden a convertir el contingut en leads, afiliació, productes digitals o serveis.</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>4) 'Monetització suggerida' + 'CTA suggerida' t'ajuden a convertir el contingut en leads, afiliació, productes digitals o serveis.</v>
+        <v>5) Recomanació: publica per mòduls complets (tema→exercici→checklist) per evitar aprenentatge aleatori.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>5) Recomanació: publica per mòduls complets (tema→exercici→checklist) per evitar aprenentatge aleatori.</v>
+        <v>Llegenda de nivells</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Nivell 0: Fonaments (conceptes imprescindibles).</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Nivell 1: Operatiu (treballar amb solvència).</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Llegenda de nivells</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Nivell 0: Fonaments (conceptes imprescindibles).</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Nivell 1: Operatiu (treballar amb solvència).</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
         <v>Nivell 2: Avançat (criteri professional i projectes).</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A11"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2267,7 +2266,7 @@
         <v>Acústica i percepció</v>
       </c>
       <c r="F2" t="str">
-        <v>El so: propagació, freqüència i representació.</v>
+        <v>El so: propagació, freqüència i representació</v>
       </c>
       <c r="G2" t="str">
         <v>Entendre el so com una ona i què implica fase i polaritat.</v>
@@ -2352,6 +2351,9 @@
       <c r="P3" t="str">
         <v/>
       </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -2402,6 +2404,9 @@
       <c r="P4" t="str">
         <v/>
       </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -2452,6 +2457,9 @@
       <c r="P5" t="str">
         <v/>
       </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -2502,6 +2510,9 @@
       <c r="P6" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -2552,6 +2563,9 @@
       <c r="P7" t="str">
         <v/>
       </c>
+      <c r="Q7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -2602,6 +2616,9 @@
       <c r="P8" t="str">
         <v/>
       </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -2652,6 +2669,9 @@
       <c r="P9" t="str">
         <v/>
       </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -2702,6 +2722,9 @@
       <c r="P10" t="str">
         <v/>
       </c>
+      <c r="Q10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -2752,6 +2775,9 @@
       <c r="P11" t="str">
         <v/>
       </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -2802,6 +2828,9 @@
       <c r="P12" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -2852,6 +2881,9 @@
       <c r="P13" t="str">
         <v>Punt natural per ingressos passius; afegeix upsell a consultoria.</v>
       </c>
+      <c r="Q13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -2902,6 +2934,9 @@
       <c r="P14" t="str">
         <v/>
       </c>
+      <c r="Q14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -2952,6 +2987,9 @@
       <c r="P15" t="str">
         <v/>
       </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -3002,6 +3040,9 @@
       <c r="P16" t="str">
         <v/>
       </c>
+      <c r="Q16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -3052,6 +3093,9 @@
       <c r="P17" t="str">
         <v/>
       </c>
+      <c r="Q17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -3102,6 +3146,9 @@
       <c r="P18" t="str">
         <v/>
       </c>
+      <c r="Q18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -3152,6 +3199,9 @@
       <c r="P19" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -3202,6 +3252,9 @@
       <c r="P20" t="str">
         <v>Punt natural per ingressos passius; afegeix upsell a consultoria.</v>
       </c>
+      <c r="Q20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -3252,6 +3305,9 @@
       <c r="P21" t="str">
         <v/>
       </c>
+      <c r="Q21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -3302,6 +3358,9 @@
       <c r="P22" t="str">
         <v/>
       </c>
+      <c r="Q22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -3352,6 +3411,9 @@
       <c r="P23" t="str">
         <v/>
       </c>
+      <c r="Q23" t="str">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -3402,6 +3464,9 @@
       <c r="P24" t="str">
         <v/>
       </c>
+      <c r="Q24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -3452,6 +3517,9 @@
       <c r="P25" t="str">
         <v/>
       </c>
+      <c r="Q25" t="str">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -3502,6 +3570,9 @@
       <c r="P26" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q26" t="str">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -3552,6 +3623,9 @@
       <c r="P27" t="str">
         <v>Punt natural per ingressos passius; afegeix upsell a consultoria.</v>
       </c>
+      <c r="Q27" t="str">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -3602,6 +3676,9 @@
       <c r="P28" t="str">
         <v/>
       </c>
+      <c r="Q28" t="str">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -3652,6 +3729,9 @@
       <c r="P29" t="str">
         <v/>
       </c>
+      <c r="Q29" t="str">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -3702,6 +3782,9 @@
       <c r="P30" t="str">
         <v/>
       </c>
+      <c r="Q30" t="str">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -3752,6 +3835,9 @@
       <c r="P31" t="str">
         <v/>
       </c>
+      <c r="Q31" t="str">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -3802,6 +3888,9 @@
       <c r="P32" t="str">
         <v/>
       </c>
+      <c r="Q32" t="str">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -3852,6 +3941,9 @@
       <c r="P33" t="str">
         <v/>
       </c>
+      <c r="Q33" t="str">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -3902,6 +3994,9 @@
       <c r="P34" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q34" t="str">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -3952,6 +4047,9 @@
       <c r="P35" t="str">
         <v/>
       </c>
+      <c r="Q35" t="str">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -4002,6 +4100,9 @@
       <c r="P36" t="str">
         <v/>
       </c>
+      <c r="Q36" t="str">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -4052,6 +4153,9 @@
       <c r="P37" t="str">
         <v/>
       </c>
+      <c r="Q37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -4102,6 +4206,9 @@
       <c r="P38" t="str">
         <v/>
       </c>
+      <c r="Q38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -4152,6 +4259,9 @@
       <c r="P39" t="str">
         <v/>
       </c>
+      <c r="Q39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -4202,6 +4312,9 @@
       <c r="P40" t="str">
         <v/>
       </c>
+      <c r="Q40" t="str">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -4252,6 +4365,9 @@
       <c r="P41" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q41" t="str">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -4302,6 +4418,9 @@
       <c r="P42" t="str">
         <v>Punt natural per ingressos passius; afegeix upsell a consultoria.</v>
       </c>
+      <c r="Q42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -4352,6 +4471,9 @@
       <c r="P43" t="str">
         <v/>
       </c>
+      <c r="Q43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -4402,6 +4524,9 @@
       <c r="P44" t="str">
         <v/>
       </c>
+      <c r="Q44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -4452,6 +4577,9 @@
       <c r="P45" t="str">
         <v/>
       </c>
+      <c r="Q45" t="str">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -4502,6 +4630,9 @@
       <c r="P46" t="str">
         <v/>
       </c>
+      <c r="Q46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -4552,6 +4683,9 @@
       <c r="P47" t="str">
         <v/>
       </c>
+      <c r="Q47" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -4602,6 +4736,9 @@
       <c r="P48" t="str">
         <v/>
       </c>
+      <c r="Q48" t="str">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -4652,6 +4789,9 @@
       <c r="P49" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q49" t="str">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -4702,6 +4842,9 @@
       <c r="P50" t="str">
         <v>Punt natural per ingressos passius; afegeix upsell a consultoria.</v>
       </c>
+      <c r="Q50" t="str">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -4752,6 +4895,9 @@
       <c r="P51" t="str">
         <v/>
       </c>
+      <c r="Q51" t="str">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -4802,6 +4948,9 @@
       <c r="P52" t="str">
         <v/>
       </c>
+      <c r="Q52" t="str">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -4852,6 +5001,9 @@
       <c r="P53" t="str">
         <v/>
       </c>
+      <c r="Q53" t="str">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -4902,6 +5054,9 @@
       <c r="P54" t="str">
         <v/>
       </c>
+      <c r="Q54" t="str">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55">
@@ -4952,6 +5107,9 @@
       <c r="P55" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q55" t="str">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -5002,6 +5160,9 @@
       <c r="P56" t="str">
         <v>Punt natural per ingressos passius; afegeix upsell a consultoria.</v>
       </c>
+      <c r="Q56" t="str">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -5052,6 +5213,9 @@
       <c r="P57" t="str">
         <v/>
       </c>
+      <c r="Q57" t="str">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58">
@@ -5102,6 +5266,9 @@
       <c r="P58" t="str">
         <v/>
       </c>
+      <c r="Q58" t="str">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59">
@@ -5152,6 +5319,9 @@
       <c r="P59" t="str">
         <v/>
       </c>
+      <c r="Q59" t="str">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60">
@@ -5202,6 +5372,9 @@
       <c r="P60" t="str">
         <v/>
       </c>
+      <c r="Q60" t="str">
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61">
@@ -5252,6 +5425,9 @@
       <c r="P61" t="str">
         <v/>
       </c>
+      <c r="Q61" t="str">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62">
@@ -5302,6 +5478,9 @@
       <c r="P62" t="str">
         <v/>
       </c>
+      <c r="Q62" t="str">
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63">
@@ -5352,6 +5531,9 @@
       <c r="P63" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q63" t="str">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64">
@@ -5402,6 +5584,9 @@
       <c r="P64" t="str">
         <v>Punt natural per ingressos passius; afegeix upsell a consultoria.</v>
       </c>
+      <c r="Q64" t="str">
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65">
@@ -5452,6 +5637,9 @@
       <c r="P65" t="str">
         <v/>
       </c>
+      <c r="Q65" t="str">
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66">
@@ -5502,6 +5690,9 @@
       <c r="P66" t="str">
         <v/>
       </c>
+      <c r="Q66" t="str">
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67">
@@ -5552,6 +5743,9 @@
       <c r="P67" t="str">
         <v/>
       </c>
+      <c r="Q67" t="str">
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68">
@@ -5602,6 +5796,9 @@
       <c r="P68" t="str">
         <v/>
       </c>
+      <c r="Q68" t="str">
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69">
@@ -5652,6 +5849,9 @@
       <c r="P69" t="str">
         <v/>
       </c>
+      <c r="Q69" t="str">
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70">
@@ -5702,6 +5902,9 @@
       <c r="P70" t="str">
         <v/>
       </c>
+      <c r="Q70" t="str">
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71">
@@ -5752,6 +5955,9 @@
       <c r="P71" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q71" t="str">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72">
@@ -5802,6 +6008,9 @@
       <c r="P72" t="str">
         <v>Punt natural per ingressos passius; afegeix upsell a consultoria.</v>
       </c>
+      <c r="Q72" t="str">
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73">
@@ -5852,6 +6061,9 @@
       <c r="P73" t="str">
         <v/>
       </c>
+      <c r="Q73" t="str">
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74">
@@ -5902,6 +6114,9 @@
       <c r="P74" t="str">
         <v/>
       </c>
+      <c r="Q74" t="str">
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75">
@@ -5952,6 +6167,9 @@
       <c r="P75" t="str">
         <v/>
       </c>
+      <c r="Q75" t="str">
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76">
@@ -6002,6 +6220,9 @@
       <c r="P76" t="str">
         <v/>
       </c>
+      <c r="Q76" t="str">
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77">
@@ -6052,6 +6273,9 @@
       <c r="P77" t="str">
         <v/>
       </c>
+      <c r="Q77" t="str">
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78">
@@ -6102,6 +6326,9 @@
       <c r="P78" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q78" t="str">
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79">
@@ -6152,6 +6379,9 @@
       <c r="P79" t="str">
         <v>Punt natural per ingressos passius; afegeix upsell a consultoria.</v>
       </c>
+      <c r="Q79" t="str">
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80">
@@ -6202,6 +6432,9 @@
       <c r="P80" t="str">
         <v/>
       </c>
+      <c r="Q80" t="str">
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81">
@@ -6252,6 +6485,9 @@
       <c r="P81" t="str">
         <v/>
       </c>
+      <c r="Q81" t="str">
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82">
@@ -6302,6 +6538,9 @@
       <c r="P82" t="str">
         <v/>
       </c>
+      <c r="Q82" t="str">
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83">
@@ -6352,6 +6591,9 @@
       <c r="P83" t="str">
         <v/>
       </c>
+      <c r="Q83" t="str">
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84">
@@ -6402,6 +6644,9 @@
       <c r="P84" t="str">
         <v/>
       </c>
+      <c r="Q84" t="str">
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85">
@@ -6452,6 +6697,9 @@
       <c r="P85" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q85" t="str">
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86">
@@ -6502,6 +6750,9 @@
       <c r="P86" t="str">
         <v>Punt natural per ingressos passius; afegeix upsell a consultoria.</v>
       </c>
+      <c r="Q86" t="str">
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87">
@@ -6552,6 +6803,9 @@
       <c r="P87" t="str">
         <v/>
       </c>
+      <c r="Q87" t="str">
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88">
@@ -6602,6 +6856,9 @@
       <c r="P88" t="str">
         <v/>
       </c>
+      <c r="Q88" t="str">
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89">
@@ -6652,6 +6909,9 @@
       <c r="P89" t="str">
         <v/>
       </c>
+      <c r="Q89" t="str">
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90">
@@ -6702,6 +6962,9 @@
       <c r="P90" t="str">
         <v/>
       </c>
+      <c r="Q90" t="str">
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91">
@@ -6752,6 +7015,9 @@
       <c r="P91" t="str">
         <v/>
       </c>
+      <c r="Q91" t="str">
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92">
@@ -6802,6 +7068,9 @@
       <c r="P92" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q92" t="str">
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93">
@@ -6852,6 +7121,9 @@
       <c r="P93" t="str">
         <v>Punt natural per ingressos passius; afegeix upsell a consultoria.</v>
       </c>
+      <c r="Q93" t="str">
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94">
@@ -6902,6 +7174,9 @@
       <c r="P94" t="str">
         <v/>
       </c>
+      <c r="Q94" t="str">
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95">
@@ -6952,6 +7227,9 @@
       <c r="P95" t="str">
         <v/>
       </c>
+      <c r="Q95" t="str">
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96">
@@ -7002,6 +7280,9 @@
       <c r="P96" t="str">
         <v/>
       </c>
+      <c r="Q96" t="str">
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97">
@@ -7052,6 +7333,9 @@
       <c r="P97" t="str">
         <v/>
       </c>
+      <c r="Q97" t="str">
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98">
@@ -7102,6 +7386,9 @@
       <c r="P98" t="str">
         <v/>
       </c>
+      <c r="Q98" t="str">
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99">
@@ -7152,6 +7439,9 @@
       <c r="P99" t="str">
         <v/>
       </c>
+      <c r="Q99" t="str">
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100">
@@ -7202,6 +7492,9 @@
       <c r="P100" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q100" t="str">
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101">
@@ -7252,6 +7545,9 @@
       <c r="P101" t="str">
         <v>Punt natural per ingressos passius; afegeix upsell a consultoria.</v>
       </c>
+      <c r="Q101" t="str">
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102">
@@ -7302,6 +7598,9 @@
       <c r="P102" t="str">
         <v/>
       </c>
+      <c r="Q102" t="str">
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103">
@@ -7352,6 +7651,9 @@
       <c r="P103" t="str">
         <v/>
       </c>
+      <c r="Q103" t="str">
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104">
@@ -7402,6 +7704,9 @@
       <c r="P104" t="str">
         <v/>
       </c>
+      <c r="Q104" t="str">
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105">
@@ -7452,6 +7757,9 @@
       <c r="P105" t="str">
         <v/>
       </c>
+      <c r="Q105" t="str">
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106">
@@ -7502,6 +7810,9 @@
       <c r="P106" t="str">
         <v/>
       </c>
+      <c r="Q106" t="str">
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107">
@@ -7552,6 +7863,9 @@
       <c r="P107" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q107" t="str">
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108">
@@ -7602,6 +7916,9 @@
       <c r="P108" t="str">
         <v>Punt natural per ingressos passius; afegeix upsell a consultoria.</v>
       </c>
+      <c r="Q108" t="str">
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109">
@@ -7652,6 +7969,9 @@
       <c r="P109" t="str">
         <v/>
       </c>
+      <c r="Q109" t="str">
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110">
@@ -7702,6 +8022,9 @@
       <c r="P110" t="str">
         <v/>
       </c>
+      <c r="Q110" t="str">
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111">
@@ -7752,6 +8075,9 @@
       <c r="P111" t="str">
         <v/>
       </c>
+      <c r="Q111" t="str">
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112">
@@ -7802,6 +8128,9 @@
       <c r="P112" t="str">
         <v/>
       </c>
+      <c r="Q112" t="str">
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113">
@@ -7852,6 +8181,9 @@
       <c r="P113" t="str">
         <v/>
       </c>
+      <c r="Q113" t="str">
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114">
@@ -7902,6 +8234,9 @@
       <c r="P114" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q114" t="str">
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115">
@@ -7952,6 +8287,9 @@
       <c r="P115" t="str">
         <v>Punt natural per ingressos passius; afegeix upsell a consultoria.</v>
       </c>
+      <c r="Q115" t="str">
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116">
@@ -8002,6 +8340,9 @@
       <c r="P116" t="str">
         <v/>
       </c>
+      <c r="Q116" t="str">
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117">
@@ -8052,6 +8393,9 @@
       <c r="P117" t="str">
         <v/>
       </c>
+      <c r="Q117" t="str">
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118">
@@ -8102,6 +8446,9 @@
       <c r="P118" t="str">
         <v/>
       </c>
+      <c r="Q118" t="str">
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119">
@@ -8152,6 +8499,9 @@
       <c r="P119" t="str">
         <v/>
       </c>
+      <c r="Q119" t="str">
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120">
@@ -8202,6 +8552,9 @@
       <c r="P120" t="str">
         <v/>
       </c>
+      <c r="Q120" t="str">
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121">
@@ -8252,6 +8605,9 @@
       <c r="P121" t="str">
         <v/>
       </c>
+      <c r="Q121" t="str">
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122">
@@ -8302,6 +8658,9 @@
       <c r="P122" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q122" t="str">
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123">
@@ -8352,6 +8711,9 @@
       <c r="P123" t="str">
         <v>Punt natural per ingressos passius; afegeix upsell a consultoria.</v>
       </c>
+      <c r="Q123" t="str">
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124">
@@ -8402,6 +8764,9 @@
       <c r="P124" t="str">
         <v/>
       </c>
+      <c r="Q124" t="str">
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125">
@@ -8452,6 +8817,9 @@
       <c r="P125" t="str">
         <v/>
       </c>
+      <c r="Q125" t="str">
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126">
@@ -8502,6 +8870,9 @@
       <c r="P126" t="str">
         <v/>
       </c>
+      <c r="Q126" t="str">
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127">
@@ -8552,6 +8923,9 @@
       <c r="P127" t="str">
         <v/>
       </c>
+      <c r="Q127" t="str">
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128">
@@ -8602,6 +8976,9 @@
       <c r="P128" t="str">
         <v/>
       </c>
+      <c r="Q128" t="str">
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129">
@@ -8652,6 +9029,9 @@
       <c r="P129" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q129" t="str">
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130">
@@ -8702,6 +9082,9 @@
       <c r="P130" t="str">
         <v>Punt natural per ingressos passius; afegeix upsell a consultoria.</v>
       </c>
+      <c r="Q130" t="str">
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131">
@@ -8752,6 +9135,9 @@
       <c r="P131" t="str">
         <v/>
       </c>
+      <c r="Q131" t="str">
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132">
@@ -8802,6 +9188,9 @@
       <c r="P132" t="str">
         <v/>
       </c>
+      <c r="Q132" t="str">
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133">
@@ -8852,6 +9241,9 @@
       <c r="P133" t="str">
         <v/>
       </c>
+      <c r="Q133" t="str">
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134">
@@ -8902,6 +9294,9 @@
       <c r="P134" t="str">
         <v/>
       </c>
+      <c r="Q134" t="str">
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135">
@@ -8952,6 +9347,9 @@
       <c r="P135" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q135" t="str">
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136">
@@ -9002,6 +9400,9 @@
       <c r="P136" t="str">
         <v>Punt natural per ingressos passius; afegeix upsell a consultoria.</v>
       </c>
+      <c r="Q136" t="str">
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137">
@@ -9052,6 +9453,9 @@
       <c r="P137" t="str">
         <v/>
       </c>
+      <c r="Q137" t="str">
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138">
@@ -9102,6 +9506,9 @@
       <c r="P138" t="str">
         <v/>
       </c>
+      <c r="Q138" t="str">
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139">
@@ -9152,6 +9559,9 @@
       <c r="P139" t="str">
         <v/>
       </c>
+      <c r="Q139" t="str">
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140">
@@ -9202,6 +9612,9 @@
       <c r="P140" t="str">
         <v/>
       </c>
+      <c r="Q140" t="str">
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141">
@@ -9252,6 +9665,9 @@
       <c r="P141" t="str">
         <v/>
       </c>
+      <c r="Q141" t="str">
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142">
@@ -9302,6 +9718,9 @@
       <c r="P142" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q142" t="str">
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143">
@@ -9352,6 +9771,9 @@
       <c r="P143" t="str">
         <v>Punt natural per ingressos passius; afegeix upsell a consultoria.</v>
       </c>
+      <c r="Q143" t="str">
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144">
@@ -9402,6 +9824,9 @@
       <c r="P144" t="str">
         <v/>
       </c>
+      <c r="Q144" t="str">
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145">
@@ -9452,6 +9877,9 @@
       <c r="P145" t="str">
         <v/>
       </c>
+      <c r="Q145" t="str">
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146">
@@ -9502,6 +9930,9 @@
       <c r="P146" t="str">
         <v/>
       </c>
+      <c r="Q146" t="str">
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147">
@@ -9552,6 +9983,9 @@
       <c r="P147" t="str">
         <v/>
       </c>
+      <c r="Q147" t="str">
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148">
@@ -9602,6 +10036,9 @@
       <c r="P148" t="str">
         <v/>
       </c>
+      <c r="Q148" t="str">
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149">
@@ -9652,6 +10089,9 @@
       <c r="P149" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q149" t="str">
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150">
@@ -9702,6 +10142,9 @@
       <c r="P150" t="str">
         <v>Punt natural per ingressos passius; afegeix upsell a consultoria.</v>
       </c>
+      <c r="Q150" t="str">
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151">
@@ -9752,6 +10195,9 @@
       <c r="P151" t="str">
         <v/>
       </c>
+      <c r="Q151" t="str">
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152">
@@ -9802,6 +10248,9 @@
       <c r="P152" t="str">
         <v/>
       </c>
+      <c r="Q152" t="str">
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153">
@@ -9852,6 +10301,9 @@
       <c r="P153" t="str">
         <v/>
       </c>
+      <c r="Q153" t="str">
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154">
@@ -9902,6 +10354,9 @@
       <c r="P154" t="str">
         <v/>
       </c>
+      <c r="Q154" t="str">
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155">
@@ -9952,6 +10407,9 @@
       <c r="P155" t="str">
         <v/>
       </c>
+      <c r="Q155" t="str">
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156">
@@ -10002,6 +10460,9 @@
       <c r="P156" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q156" t="str">
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157">
@@ -10052,6 +10513,9 @@
       <c r="P157" t="str">
         <v>Punt natural per ingressos passius; afegeix upsell a consultoria.</v>
       </c>
+      <c r="Q157" t="str">
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158">
@@ -10102,6 +10566,9 @@
       <c r="P158" t="str">
         <v/>
       </c>
+      <c r="Q158" t="str">
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159">
@@ -10152,6 +10619,9 @@
       <c r="P159" t="str">
         <v/>
       </c>
+      <c r="Q159" t="str">
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160">
@@ -10202,6 +10672,9 @@
       <c r="P160" t="str">
         <v/>
       </c>
+      <c r="Q160" t="str">
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161">
@@ -10252,6 +10725,9 @@
       <c r="P161" t="str">
         <v/>
       </c>
+      <c r="Q161" t="str">
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162">
@@ -10302,6 +10778,9 @@
       <c r="P162" t="str">
         <v/>
       </c>
+      <c r="Q162" t="str">
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163">
@@ -10352,6 +10831,9 @@
       <c r="P163" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q163" t="str">
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164">
@@ -10402,6 +10884,9 @@
       <c r="P164" t="str">
         <v>Punt natural per ingressos passius; afegeix upsell a consultoria.</v>
       </c>
+      <c r="Q164" t="str">
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165">
@@ -10452,6 +10937,9 @@
       <c r="P165" t="str">
         <v/>
       </c>
+      <c r="Q165" t="str">
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166">
@@ -10502,6 +10990,9 @@
       <c r="P166" t="str">
         <v/>
       </c>
+      <c r="Q166" t="str">
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167">
@@ -10552,6 +11043,9 @@
       <c r="P167" t="str">
         <v/>
       </c>
+      <c r="Q167" t="str">
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168">
@@ -10602,6 +11096,9 @@
       <c r="P168" t="str">
         <v/>
       </c>
+      <c r="Q168" t="str">
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169">
@@ -10652,6 +11149,9 @@
       <c r="P169" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q169" t="str">
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170">
@@ -10702,6 +11202,9 @@
       <c r="P170" t="str">
         <v>Punt natural per ingressos passius; afegeix upsell a consultoria.</v>
       </c>
+      <c r="Q170" t="str">
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171">
@@ -10752,6 +11255,9 @@
       <c r="P171" t="str">
         <v/>
       </c>
+      <c r="Q171" t="str">
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172">
@@ -10802,6 +11308,9 @@
       <c r="P172" t="str">
         <v/>
       </c>
+      <c r="Q172" t="str">
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173">
@@ -10852,6 +11361,9 @@
       <c r="P173" t="str">
         <v/>
       </c>
+      <c r="Q173" t="str">
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174">
@@ -10902,6 +11414,9 @@
       <c r="P174" t="str">
         <v/>
       </c>
+      <c r="Q174" t="str">
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175">
@@ -10952,6 +11467,9 @@
       <c r="P175" t="str">
         <v/>
       </c>
+      <c r="Q175" t="str">
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176">
@@ -11002,6 +11520,9 @@
       <c r="P176" t="str">
         <v/>
       </c>
+      <c r="Q176" t="str">
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177">
@@ -11052,6 +11573,9 @@
       <c r="P177" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q177" t="str">
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178">
@@ -11102,6 +11626,9 @@
       <c r="P178" t="str">
         <v>Punt natural per ingressos passius; afegeix upsell a consultoria.</v>
       </c>
+      <c r="Q178" t="str">
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="A179">
@@ -11152,6 +11679,9 @@
       <c r="P179" t="str">
         <v/>
       </c>
+      <c r="Q179" t="str">
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180">
@@ -11202,6 +11732,9 @@
       <c r="P180" t="str">
         <v/>
       </c>
+      <c r="Q180" t="str">
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181">
@@ -11252,6 +11785,9 @@
       <c r="P181" t="str">
         <v/>
       </c>
+      <c r="Q181" t="str">
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182">
@@ -11302,6 +11838,9 @@
       <c r="P182" t="str">
         <v/>
       </c>
+      <c r="Q182" t="str">
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183">
@@ -11352,6 +11891,9 @@
       <c r="P183" t="str">
         <v/>
       </c>
+      <c r="Q183" t="str">
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184">
@@ -11402,6 +11944,9 @@
       <c r="P184" t="str">
         <v/>
       </c>
+      <c r="Q184" t="str">
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185">
@@ -11452,6 +11997,9 @@
       <c r="P185" t="str">
         <v/>
       </c>
+      <c r="Q185" t="str">
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186">
@@ -11502,6 +12050,9 @@
       <c r="P186" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q186" t="str">
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187">
@@ -11552,6 +12103,9 @@
       <c r="P187" t="str">
         <v>Punt natural per ingressos passius; afegeix upsell a consultoria.</v>
       </c>
+      <c r="Q187" t="str">
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188">
@@ -11602,6 +12156,9 @@
       <c r="P188" t="str">
         <v/>
       </c>
+      <c r="Q188" t="str">
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189">
@@ -11652,6 +12209,9 @@
       <c r="P189" t="str">
         <v/>
       </c>
+      <c r="Q189" t="str">
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190">
@@ -11702,6 +12262,9 @@
       <c r="P190" t="str">
         <v/>
       </c>
+      <c r="Q190" t="str">
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191">
@@ -11752,6 +12315,9 @@
       <c r="P191" t="str">
         <v/>
       </c>
+      <c r="Q191" t="str">
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192">
@@ -11802,6 +12368,9 @@
       <c r="P192" t="str">
         <v/>
       </c>
+      <c r="Q192" t="str">
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193">
@@ -11852,6 +12421,9 @@
       <c r="P193" t="str">
         <v/>
       </c>
+      <c r="Q193" t="str">
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194">
@@ -11902,6 +12474,9 @@
       <c r="P194" t="str">
         <v/>
       </c>
+      <c r="Q194" t="str">
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195">
@@ -11952,6 +12527,9 @@
       <c r="P195" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q195" t="str">
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196">
@@ -12002,6 +12580,9 @@
       <c r="P196" t="str">
         <v>Punt natural per ingressos passius; afegeix upsell a consultoria.</v>
       </c>
+      <c r="Q196" t="str">
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197">
@@ -12052,6 +12633,9 @@
       <c r="P197" t="str">
         <v/>
       </c>
+      <c r="Q197" t="str">
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198">
@@ -12102,6 +12686,9 @@
       <c r="P198" t="str">
         <v/>
       </c>
+      <c r="Q198" t="str">
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199">
@@ -12152,6 +12739,9 @@
       <c r="P199" t="str">
         <v/>
       </c>
+      <c r="Q199" t="str">
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200">
@@ -12202,6 +12792,9 @@
       <c r="P200" t="str">
         <v/>
       </c>
+      <c r="Q200" t="str">
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201">
@@ -12252,6 +12845,9 @@
       <c r="P201" t="str">
         <v/>
       </c>
+      <c r="Q201" t="str">
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202">
@@ -12302,6 +12898,9 @@
       <c r="P202" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q202" t="str">
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="A203">
@@ -12352,6 +12951,9 @@
       <c r="P203" t="str">
         <v>Punt natural per ingressos passius; afegeix upsell a consultoria.</v>
       </c>
+      <c r="Q203" t="str">
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="A204">
@@ -12402,6 +13004,9 @@
       <c r="P204" t="str">
         <v/>
       </c>
+      <c r="Q204" t="str">
+        <v/>
+      </c>
     </row>
     <row r="205">
       <c r="A205">
@@ -12452,6 +13057,9 @@
       <c r="P205" t="str">
         <v/>
       </c>
+      <c r="Q205" t="str">
+        <v/>
+      </c>
     </row>
     <row r="206">
       <c r="A206">
@@ -12502,6 +13110,9 @@
       <c r="P206" t="str">
         <v/>
       </c>
+      <c r="Q206" t="str">
+        <v/>
+      </c>
     </row>
     <row r="207">
       <c r="A207">
@@ -12552,6 +13163,9 @@
       <c r="P207" t="str">
         <v/>
       </c>
+      <c r="Q207" t="str">
+        <v/>
+      </c>
     </row>
     <row r="208">
       <c r="A208">
@@ -12602,6 +13216,9 @@
       <c r="P208" t="str">
         <v/>
       </c>
+      <c r="Q208" t="str">
+        <v/>
+      </c>
     </row>
     <row r="209">
       <c r="A209">
@@ -12652,6 +13269,9 @@
       <c r="P209" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q209" t="str">
+        <v/>
+      </c>
     </row>
     <row r="210">
       <c r="A210">
@@ -12702,6 +13322,9 @@
       <c r="P210" t="str">
         <v>Punt natural per ingressos passius; afegeix upsell a consultoria.</v>
       </c>
+      <c r="Q210" t="str">
+        <v/>
+      </c>
     </row>
     <row r="211">
       <c r="A211">
@@ -12752,6 +13375,9 @@
       <c r="P211" t="str">
         <v/>
       </c>
+      <c r="Q211" t="str">
+        <v/>
+      </c>
     </row>
     <row r="212">
       <c r="A212">
@@ -12802,6 +13428,9 @@
       <c r="P212" t="str">
         <v/>
       </c>
+      <c r="Q212" t="str">
+        <v/>
+      </c>
     </row>
     <row r="213">
       <c r="A213">
@@ -12852,6 +13481,9 @@
       <c r="P213" t="str">
         <v/>
       </c>
+      <c r="Q213" t="str">
+        <v/>
+      </c>
     </row>
     <row r="214">
       <c r="A214">
@@ -12902,6 +13534,9 @@
       <c r="P214" t="str">
         <v/>
       </c>
+      <c r="Q214" t="str">
+        <v/>
+      </c>
     </row>
     <row r="215">
       <c r="A215">
@@ -12952,6 +13587,9 @@
       <c r="P215" t="str">
         <v/>
       </c>
+      <c r="Q215" t="str">
+        <v/>
+      </c>
     </row>
     <row r="216">
       <c r="A216">
@@ -13002,6 +13640,9 @@
       <c r="P216" t="str">
         <v/>
       </c>
+      <c r="Q216" t="str">
+        <v/>
+      </c>
     </row>
     <row r="217">
       <c r="A217">
@@ -13052,6 +13693,9 @@
       <c r="P217" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q217" t="str">
+        <v/>
+      </c>
     </row>
     <row r="218">
       <c r="A218">
@@ -13102,6 +13746,9 @@
       <c r="P218" t="str">
         <v>Punt natural per ingressos passius; afegeix upsell a consultoria.</v>
       </c>
+      <c r="Q218" t="str">
+        <v/>
+      </c>
     </row>
     <row r="219">
       <c r="A219">
@@ -13152,6 +13799,9 @@
       <c r="P219" t="str">
         <v/>
       </c>
+      <c r="Q219" t="str">
+        <v/>
+      </c>
     </row>
     <row r="220">
       <c r="A220">
@@ -13202,6 +13852,9 @@
       <c r="P220" t="str">
         <v/>
       </c>
+      <c r="Q220" t="str">
+        <v/>
+      </c>
     </row>
     <row r="221">
       <c r="A221">
@@ -13252,6 +13905,9 @@
       <c r="P221" t="str">
         <v/>
       </c>
+      <c r="Q221" t="str">
+        <v/>
+      </c>
     </row>
     <row r="222">
       <c r="A222">
@@ -13302,6 +13958,9 @@
       <c r="P222" t="str">
         <v/>
       </c>
+      <c r="Q222" t="str">
+        <v/>
+      </c>
     </row>
     <row r="223">
       <c r="A223">
@@ -13352,6 +14011,9 @@
       <c r="P223" t="str">
         <v/>
       </c>
+      <c r="Q223" t="str">
+        <v/>
+      </c>
     </row>
     <row r="224">
       <c r="A224">
@@ -13402,6 +14064,9 @@
       <c r="P224" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q224" t="str">
+        <v/>
+      </c>
     </row>
     <row r="225">
       <c r="A225">
@@ -13452,6 +14117,9 @@
       <c r="P225" t="str">
         <v>Punt natural per ingressos passius; afegeix upsell a consultoria.</v>
       </c>
+      <c r="Q225" t="str">
+        <v/>
+      </c>
     </row>
     <row r="226">
       <c r="A226">
@@ -13502,6 +14170,9 @@
       <c r="P226" t="str">
         <v/>
       </c>
+      <c r="Q226" t="str">
+        <v/>
+      </c>
     </row>
     <row r="227">
       <c r="A227">
@@ -13552,6 +14223,9 @@
       <c r="P227" t="str">
         <v/>
       </c>
+      <c r="Q227" t="str">
+        <v/>
+      </c>
     </row>
     <row r="228">
       <c r="A228">
@@ -13602,6 +14276,9 @@
       <c r="P228" t="str">
         <v/>
       </c>
+      <c r="Q228" t="str">
+        <v/>
+      </c>
     </row>
     <row r="229">
       <c r="A229">
@@ -13652,6 +14329,9 @@
       <c r="P229" t="str">
         <v/>
       </c>
+      <c r="Q229" t="str">
+        <v/>
+      </c>
     </row>
     <row r="230">
       <c r="A230">
@@ -13702,6 +14382,9 @@
       <c r="P230" t="str">
         <v/>
       </c>
+      <c r="Q230" t="str">
+        <v/>
+      </c>
     </row>
     <row r="231">
       <c r="A231">
@@ -13752,6 +14435,9 @@
       <c r="P231" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q231" t="str">
+        <v/>
+      </c>
     </row>
     <row r="232">
       <c r="A232">
@@ -13802,6 +14488,9 @@
       <c r="P232" t="str">
         <v>Punt natural per ingressos passius; afegeix upsell a consultoria.</v>
       </c>
+      <c r="Q232" t="str">
+        <v/>
+      </c>
     </row>
     <row r="233">
       <c r="A233">
@@ -13852,6 +14541,9 @@
       <c r="P233" t="str">
         <v/>
       </c>
+      <c r="Q233" t="str">
+        <v/>
+      </c>
     </row>
     <row r="234">
       <c r="A234">
@@ -13902,6 +14594,9 @@
       <c r="P234" t="str">
         <v/>
       </c>
+      <c r="Q234" t="str">
+        <v/>
+      </c>
     </row>
     <row r="235">
       <c r="A235">
@@ -13952,6 +14647,9 @@
       <c r="P235" t="str">
         <v/>
       </c>
+      <c r="Q235" t="str">
+        <v/>
+      </c>
     </row>
     <row r="236">
       <c r="A236">
@@ -14002,6 +14700,9 @@
       <c r="P236" t="str">
         <v/>
       </c>
+      <c r="Q236" t="str">
+        <v/>
+      </c>
     </row>
     <row r="237">
       <c r="A237">
@@ -14052,6 +14753,9 @@
       <c r="P237" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q237" t="str">
+        <v/>
+      </c>
     </row>
     <row r="238">
       <c r="A238">
@@ -14102,6 +14806,9 @@
       <c r="P238" t="str">
         <v>Punt natural per ingressos passius; afegeix upsell a consultoria.</v>
       </c>
+      <c r="Q238" t="str">
+        <v/>
+      </c>
     </row>
     <row r="239">
       <c r="A239">
@@ -14152,6 +14859,9 @@
       <c r="P239" t="str">
         <v/>
       </c>
+      <c r="Q239" t="str">
+        <v/>
+      </c>
     </row>
     <row r="240">
       <c r="A240">
@@ -14202,6 +14912,9 @@
       <c r="P240" t="str">
         <v/>
       </c>
+      <c r="Q240" t="str">
+        <v/>
+      </c>
     </row>
     <row r="241">
       <c r="A241">
@@ -14252,6 +14965,9 @@
       <c r="P241" t="str">
         <v/>
       </c>
+      <c r="Q241" t="str">
+        <v/>
+      </c>
     </row>
     <row r="242">
       <c r="A242">
@@ -14302,6 +15018,9 @@
       <c r="P242" t="str">
         <v>Ideal per captar email i segmentar interessos.</v>
       </c>
+      <c r="Q242" t="str">
+        <v/>
+      </c>
     </row>
     <row r="243">
       <c r="A243">
@@ -14351,6 +15070,9 @@
       </c>
       <c r="P243" t="str">
         <v>Punt natural per ingressos passius; afegeix upsell a consultoria.</v>
+      </c>
+      <c r="Q243" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -14431,7 +15153,7 @@
         <v>Acústica i percepció</v>
       </c>
       <c r="F2" t="str">
-        <v>Què és el so (ona, fase, pressió)</v>
+        <v>El so: propagació, freqüència i representació</v>
       </c>
       <c r="G2" t="str">
         <v>Entendre el so com una ona i què implica fase i polaritat.</v>
